--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_monthly.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -982,38 +982,42 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39442</v>
+        <v>43880</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>44848</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40533</v>
+        <v>45456</v>
       </c>
       <c r="M4" t="n">
-        <v>753</v>
+        <v>1087</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4131976008746485</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4131976008746485</v>
       </c>
       <c r="P4" t="n">
-        <v>752</v>
+        <v>1086</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1599384989554068</v>
+        <v>0.2713351850088813</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -1023,64 +1027,64 @@
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>301</v>
+        <v>670</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4131976008746485</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4131976008746485</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>452</v>
+        <v>417</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>0.5986632950171407</v>
+        <v>0.7041511784725716</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,32 +1141,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43880</v>
+        <v>36614</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>44848</v>
+        <v>37460</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>45456</v>
+        <v>38994</v>
       </c>
       <c r="M5" t="n">
-        <v>1087</v>
+        <v>1638</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.4131976008746485</v>
+        <v>-0.4380050570761583</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.4131976008746485</v>
+        <v>-0.4380050570761583</v>
       </c>
       <c r="P5" t="n">
-        <v>1086</v>
+        <v>1637</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2713351850088813</v>
+        <v>0.220316748671827</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
@@ -1172,25 +1176,25 @@
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>670</v>
+        <v>579</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>-0.4131976008746485</v>
+        <v>-0.4380050570761583</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-0.4131976008746485</v>
+        <v>-0.4380050570761583</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>417</v>
+        <v>1059</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>0.7041511784725716</v>
+        <v>0.7793754420589409</v>
       </c>
       <c r="AD5" s="3" t="n">
         <v>0.6666666666666666</v>
@@ -1209,11 +1213,11 @@
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
@@ -1233,11 +1237,11 @@
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1273,49 +1277,45 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>36614</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>37664</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>38994</v>
+        <v>41568</v>
       </c>
       <c r="M6" t="n">
-        <v>1638</v>
+        <v>3411</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4380050570761583</v>
+        <v>-0.609877450557176</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4380050570761583</v>
+        <v>-0.609877450557176</v>
       </c>
       <c r="P6" t="n">
-        <v>1637</v>
+        <v>3410</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.220316748671827</v>
+        <v>0.3755500266655417</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -1325,98 +1325,80 @@
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>579</v>
+        <v>720</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>-0.4380050570761583</v>
+        <v>-0.609877450557176</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.4380050570761583</v>
+        <v>-0.609877450557176</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1059</v>
+        <v>2691</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>0.7793754420589409</v>
+        <v>1.563297100944838</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AP6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1426,7 +1408,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1457,32 +1439,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>36614</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37664</v>
+        <v>37460</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>41568</v>
+        <v>40654</v>
       </c>
       <c r="M7" t="n">
-        <v>3411</v>
+        <v>2783</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.609877450557176</v>
+        <v>-0.5543499163256077</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.609877450557176</v>
+        <v>-0.5543499163256077</v>
       </c>
       <c r="P7" t="n">
-        <v>3410</v>
+        <v>2782</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3755500266655417</v>
+        <v>0.3131144445254087</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1492,32 +1474,32 @@
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>720</v>
+        <v>579</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>-0.609877450557176</v>
+        <v>-0.5543499163256077</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.609877450557176</v>
+        <v>-0.5543499163256077</v>
       </c>
       <c r="Y7" t="b">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2691</v>
+        <v>2204</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>1.563297100944838</v>
+        <v>1.243912963630532</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
@@ -1529,11 +1511,11 @@
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
@@ -1553,11 +1535,11 @@
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1575,7 +1557,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1593,49 +1575,45 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36614</v>
+        <v>36521</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37460</v>
+        <v>37375</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40654</v>
+        <v>38397</v>
       </c>
       <c r="M8" t="n">
-        <v>2783</v>
+        <v>1290</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5543499163256077</v>
+        <v>-0.2090256659061214</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5543499163256077</v>
+        <v>-0.2090256659061214</v>
       </c>
       <c r="P8" t="n">
-        <v>2782</v>
+        <v>1289</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.3131144445254087</v>
+        <v>0.1335283023381515</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -1645,48 +1623,48 @@
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>-0.5543499163256077</v>
+        <v>-0.2090256659061214</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-0.5543499163256077</v>
+        <v>-0.2090256659061214</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2204</v>
+        <v>705</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>1.243912963630532</v>
+        <v>0.2642635252451979</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
@@ -1698,45 +1676,27 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1746,7 +1706,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1777,32 +1737,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>36521</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37375</v>
+        <v>37460</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>38397</v>
+        <v>39218</v>
       </c>
       <c r="M9" t="n">
-        <v>1290</v>
+        <v>1856</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2090256659061214</v>
+        <v>-0.4671232695897851</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.2090256659061214</v>
+        <v>-0.4671232695897851</v>
       </c>
       <c r="P9" t="n">
-        <v>1289</v>
+        <v>1855</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1335283023381515</v>
+        <v>0.2400607705330453</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1812,40 +1772,40 @@
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>585</v>
+        <v>644</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="3" t="n">
-        <v>-0.2090256659061214</v>
+        <v>-0.4671232695897851</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-0.2090256659061214</v>
+        <v>-0.4671232695897851</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>705</v>
+        <v>1212</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>0.2642635252451979</v>
+        <v>0.8766066201280511</v>
       </c>
       <c r="AD9" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>5/6</t>
-        </is>
-      </c>
-      <c r="AF9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>6/6</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
@@ -1857,11 +1817,11 @@
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1886,177 +1846,6 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36521</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>39218</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1856</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4671232695897851</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4671232695897851</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1855</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2400607705330453</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>644</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" s="3" t="n">
-        <v>-0.4671232695897851</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-0.4671232695897851</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1212</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" s="3" t="n">
-        <v>0.8766066201280511</v>
-      </c>
-      <c r="AD10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2069,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2546,7 +2335,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2556,7 +2345,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2567,41 +2356,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36811</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>37783</v>
+        <v>38415</v>
       </c>
       <c r="M4" t="n">
-        <v>806</v>
+        <v>1242</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2185683866529438</v>
+        <v>-0.2117116495671395</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.22085688806862</v>
       </c>
       <c r="P4" t="n">
-        <v>292</v>
+        <v>1238</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1252308092487745</v>
+        <v>0.1407604164514403</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.08167972914679614</v>
+        <v>0.1139416336580026</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>39364</v>
@@ -2614,35 +2407,35 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>141</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>-497</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2185683866529438</v>
+        <v>-0.2117116495671395</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.22085688806862</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>223</v>
+        <v>1101</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
         <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2797025138473266</v>
+        <v>0.2685713285638252</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.2501988828679748</v>
+        <v>-0.2179369783567683</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3166269890032911</v>
+        <v>0.3234837260890954</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
@@ -2663,7 +2456,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2694,35 +2487,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36811</v>
+        <v>37460</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>38415</v>
+        <v>38986</v>
       </c>
       <c r="M5" t="n">
-        <v>1242</v>
+        <v>1636</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2117116495671395</v>
+        <v>-0.4314086080914217</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.22085688806862</v>
+        <v>-0.4380050570761586</v>
       </c>
       <c r="P5" t="n">
-        <v>1238</v>
+        <v>1632</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1407604164514403</v>
+        <v>0.2204505869030779</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1139416336580026</v>
+        <v>0.2047867876822711</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>39364</v>
@@ -2735,35 +2528,35 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>141</v>
+        <v>583</v>
       </c>
       <c r="X5" t="n">
-        <v>-497</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2117116495671395</v>
+        <v>-0.4314086080914217</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.22085688806862</v>
+        <v>-0.4380050570761586</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1101</v>
+        <v>1053</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
         <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2685713285638252</v>
+        <v>0.7587322183041179</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.2179369783567683</v>
+        <v>-0.1270918243324998</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3234837260890954</v>
+        <v>0.1037867675648132</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
@@ -2784,7 +2577,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2802,52 +2595,46 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>38986</v>
-      </c>
+        <v>37664</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1636</v>
+        <v>1896</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4314086080914217</v>
+        <v>-0.605298363987808</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4380050570761586</v>
+        <v>-0.6098774505571757</v>
       </c>
       <c r="P6" t="n">
-        <v>1632</v>
+        <v>1893</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2204505869030779</v>
+        <v>0.430410363505689</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.2047867876822711</v>
+        <v>0.430410363505689</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>39364</v>
@@ -2856,56 +2643,50 @@
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.3180149709140817</v>
+      </c>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>724</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>86</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4314086080914217</v>
+        <v>-0.605298363987808</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4380050570761586</v>
+        <v>-0.6098774505571757</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1053</v>
+        <v>1172</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
         <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.7587322183041179</v>
+        <v>1.533559298368631</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.1270918243324998</v>
+        <v>0.09853175149091803</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1037867675648132</v>
+        <v>-0.07010298833157314</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.123107058535475</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.2128402214384779</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>830</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -2917,7 +2698,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2948,33 +2729,33 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37664</v>
+        <v>37460</v>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" t="n">
         <v>1896</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.605298363987808</v>
+        <v>-0.5491190720288466</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.6098774505571757</v>
+        <v>-0.5543499163256078</v>
       </c>
       <c r="P7" t="n">
         <v>1893</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.430410363505689</v>
+        <v>0.3461930634419392</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.430410363505689</v>
+        <v>0.3461930634419392</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>39364</v>
@@ -2986,38 +2767,38 @@
         <v>1</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>-0.3180149709140817</v>
+        <v>-0.113651832784307</v>
       </c>
       <c r="W7" t="n">
-        <v>724</v>
+        <v>583</v>
       </c>
       <c r="X7" t="n">
-        <v>86</v>
+        <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.605298363987808</v>
+        <v>-0.5491190720288466</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.6098774505571757</v>
+        <v>-0.5543499163256078</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1172</v>
+        <v>1313</v>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.533559298368631</v>
+        <v>1.217880460146627</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.09853175149091803</v>
+        <v>0.01431445142716825</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.07010298833157314</v>
+        <v>-0.0139236963726117</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
@@ -3038,7 +2819,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3056,50 +2837,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+        <v>37375</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>38232</v>
+      </c>
       <c r="M8" t="n">
-        <v>1896</v>
+        <v>1116</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5491190720288466</v>
+        <v>-0.1607561803938017</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5543499163256078</v>
+        <v>-0.1911504799548355</v>
       </c>
       <c r="P8" t="n">
-        <v>1893</v>
+        <v>1004</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.3461930634419392</v>
+        <v>0.1241029990867884</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.3461930634419392</v>
+        <v>0.09523030997169735</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>39364</v>
@@ -3108,58 +2887,54 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.113651832784307</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>583</v>
+        <v>524</v>
       </c>
       <c r="X8" t="n">
-        <v>-55</v>
+        <v>-114</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.5491190720288466</v>
+        <v>-0.1607561803938017</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.5543499163256078</v>
+        <v>-0.1911504799548355</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1313</v>
+        <v>592</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
         <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1.217880460146627</v>
+        <v>0.1915488403229872</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.01431445142716825</v>
+        <v>-0.2366483020430736</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-0.0139236963726117</v>
+        <v>0.3744391952624332</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
         <v>1</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.264513334295143</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.3305506853759028</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.08270819824638442</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.06916594252835273</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3169,7 +2944,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3200,35 +2975,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37375</v>
+        <v>37460</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>38232</v>
+        <v>38924</v>
       </c>
       <c r="M9" t="n">
-        <v>1116</v>
+        <v>1593</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1607561803938017</v>
+        <v>-0.3899810452148498</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1911504799548355</v>
+        <v>-0.4341707534324699</v>
       </c>
       <c r="P9" t="n">
-        <v>1004</v>
+        <v>1475</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1241029990867884</v>
+        <v>0.2147873729662626</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.09523030997169735</v>
+        <v>0.1968879963369338</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>39364</v>
@@ -3241,35 +3016,35 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>524</v>
+        <v>583</v>
       </c>
       <c r="X9" t="n">
-        <v>-114</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1607561803938017</v>
+        <v>-0.3899810452148498</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1911504799548355</v>
+        <v>-0.4341707534324699</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>592</v>
+        <v>1010</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
         <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1915488403229872</v>
+        <v>0.6392933238479479</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.2366483020430736</v>
+        <v>-0.1349906156778372</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3744391952624332</v>
+        <v>0.1452143304413851</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
@@ -3283,143 +3058,6 @@
         <v>0.08270819824638442</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.06916594252835273</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>38924</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1593</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3899810452148498</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4341707534324699</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1475</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2147873729662626</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1968879963369338</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>583</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-55</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.3899810452148498</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.4341707534324699</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1010</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.6392933238479479</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.1349906156778372</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.1452143304413851</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.1152082671901376</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.171412658561906</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>787</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.08270819824638442</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>-0.1361240023967677</v>
       </c>
     </row>
@@ -3434,7 +3072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3917,7 +3555,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3927,7 +3565,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3938,41 +3576,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>40765</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40533</v>
+        <v>40784</v>
       </c>
       <c r="M4" t="n">
-        <v>807</v>
+        <v>980</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.07135481844085556</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="P4" t="n">
-        <v>805</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1546755474705558</v>
+        <v>0.01516685097673147</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.08370501759350023</v>
+        <v>0.009043865044496601</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43364</v>
@@ -3985,40 +3627,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>967</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.07135481844085556</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>452</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>-408</v>
+        <v>-847</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.5983357204467421</v>
+        <v>0.07683754770692364</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03117269325661598</v>
+        <v>-0.1058338458056196</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.06315655508460816</v>
+        <v>0.3661509505119783</v>
       </c>
       <c r="AH4" t="n">
-        <v>-23</v>
+        <v>-462</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4027,8 +3669,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1461342146462365</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1068371958786292</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4038,7 +3684,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4069,35 +3715,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>40765</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>40784</v>
+        <v>40533</v>
       </c>
       <c r="M5" t="n">
-        <v>980</v>
+        <v>807</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.07135481844085556</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="P5" t="n">
-        <v>28</v>
+        <v>805</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.01516685097673147</v>
+        <v>0.1546755474705558</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.009043865044496601</v>
+        <v>0.08370501759350023</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43364</v>
@@ -4110,40 +3756,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>967</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
-        <v>612</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.07135481844085556</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>452</v>
       </c>
       <c r="AC5" t="n">
-        <v>-847</v>
+        <v>-408</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.07683754770692364</v>
+        <v>0.5983357204467421</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1058338458056196</v>
+        <v>-0.03117269325661598</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3661509505119783</v>
+        <v>0.06315655508460816</v>
       </c>
       <c r="AH5" t="n">
-        <v>-462</v>
+        <v>-23</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4156,7 +3802,7 @@
         <v>0.1461342146462365</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1068371958786292</v>
+        <v>-0.007149815379016156</v>
       </c>
     </row>
     <row r="6">
@@ -4167,7 +3813,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4185,52 +3831,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>39881</v>
+        <v>40004</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40533</v>
+        <v>40399</v>
       </c>
       <c r="M6" t="n">
-        <v>807</v>
+        <v>713</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.2064790741024939</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.2161164061045036</v>
       </c>
       <c r="P6" t="n">
-        <v>805</v>
+        <v>705</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1546755474705558</v>
+        <v>0.1080257419379396</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.08370501759350023</v>
+        <v>0.05495415235536932</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43364</v>
@@ -4243,62 +3885,50 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>441</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.2064790741024939</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.2161164061045036</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>452</v>
+        <v>272</v>
       </c>
       <c r="AC6" t="n">
-        <v>-408</v>
+        <v>-588</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5983357204467421</v>
+        <v>0.2602062117882489</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03117269325661598</v>
+        <v>-0.05992355849474688</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.06315655508460816</v>
+        <v>0.23102669485034</v>
       </c>
       <c r="AH6" t="n">
-        <v>-23</v>
+        <v>-203</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1461342146462365</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.007149815379016156</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4308,7 +3938,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4339,35 +3969,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>40004</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>40399</v>
+        <v>40462</v>
       </c>
       <c r="M7" t="n">
-        <v>713</v>
+        <v>757</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2064790741024939</v>
+        <v>-0.3609757233342479</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2161164061045036</v>
+        <v>-0.3687366895678811</v>
       </c>
       <c r="P7" t="n">
-        <v>705</v>
+        <v>749</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1080257419379396</v>
+        <v>0.1580972654520925</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05495415235536932</v>
+        <v>0.08286728510719067</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43364</v>
@@ -4380,40 +4010,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>441</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2064790741024939</v>
+        <v>-0.3609757233342479</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2161164061045036</v>
+        <v>-0.3687366895678811</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>272</v>
+        <v>402</v>
       </c>
       <c r="AC7" t="n">
-        <v>-588</v>
+        <v>-458</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2602062117882489</v>
+        <v>0.5648857743209961</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.05992355849474688</v>
+        <v>-0.03201042574292554</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.23102669485034</v>
+        <v>0.07653004561858601</v>
       </c>
       <c r="AH7" t="n">
-        <v>-203</v>
+        <v>-73</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4433,7 +4063,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4451,52 +4081,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>40416</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40462</v>
+        <v>40486</v>
       </c>
       <c r="M8" t="n">
-        <v>757</v>
+        <v>775</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.3609757233342479</v>
+        <v>-0.1513517485327929</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3687366895678811</v>
+        <v>-0.1616586033180829</v>
       </c>
       <c r="P8" t="n">
-        <v>749</v>
+        <v>767</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1580972654520925</v>
+        <v>0.0874086978492416</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.08286728510719067</v>
+        <v>0.04635639564767428</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43364</v>
@@ -4509,56 +4135,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>726</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3609757233342479</v>
+        <v>-0.1513517485327929</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3687366895678811</v>
+        <v>-0.1616586033180829</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>402</v>
+        <v>49</v>
       </c>
       <c r="AC8" t="n">
-        <v>-458</v>
+        <v>-811</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.5648857743209961</v>
+        <v>0.1783445005290762</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.03201042574292554</v>
+        <v>-0.06852131520244192</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.07653004561858601</v>
+        <v>0.286154020420041</v>
       </c>
       <c r="AH8" t="n">
-        <v>-73</v>
+        <v>-426</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.0008377324863095559</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>0.01337349053397785</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -4570,7 +4188,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4601,35 +4219,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>40416</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>40486</v>
+        <v>40466</v>
       </c>
       <c r="M9" t="n">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1513517485327929</v>
+        <v>-0.3723569839339402</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1616586033180829</v>
+        <v>-0.3799797244656153</v>
       </c>
       <c r="P9" t="n">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.0874086978492416</v>
+        <v>0.1635517543216592</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.04635639564767428</v>
+        <v>0.08595216934937883</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43364</v>
@@ -4642,40 +4260,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>726</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1513517485327929</v>
+        <v>-0.3723569839339402</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1616586033180829</v>
+        <v>-0.3799797244656153</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>49</v>
+        <v>406</v>
       </c>
       <c r="AC9" t="n">
-        <v>-811</v>
+        <v>-454</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1783445005290762</v>
+        <v>0.5932623711290519</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06852131520244192</v>
+        <v>-0.02892554150073738</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.286154020420041</v>
+        <v>0.06514878501889365</v>
       </c>
       <c r="AH9" t="n">
-        <v>-426</v>
+        <v>-69</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4686,143 +4304,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40466</v>
-      </c>
-      <c r="M10" t="n">
-        <v>761</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3723569839339402</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3799797244656153</v>
-      </c>
-      <c r="P10" t="n">
-        <v>753</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1635517543216592</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.08595216934937883</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>355</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.3723569839339402</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3799797244656153</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>406</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-454</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.5932623711290519</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.02892554150073738</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.06514878501889365</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-69</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.002247151755878599</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0.001992229934285494</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-46</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4835,7 +4316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5318,7 +4799,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5328,7 +4809,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5339,13 +4820,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -5355,25 +4840,25 @@
         <v>43458</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43563</v>
+        <v>43588</v>
       </c>
       <c r="M4" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1972404039901224</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1989196555792887</v>
       </c>
       <c r="P4" t="n">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04849898132196487</v>
+        <v>0.07930286943495034</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.03006079347508416</v>
+        <v>0.05230553290603873</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43880</v>
@@ -5392,34 +4877,34 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1972404039901224</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1989196555792887</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1574905164302043</v>
+        <v>0.2457029538737467</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.02224473943095457</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.0611783678916169</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5439,7 +4924,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5470,7 +4955,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -5564,7 +5049,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5582,52 +5067,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>43402</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43588</v>
+        <v>43565</v>
       </c>
       <c r="M6" t="n">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.08992794834420026</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.09183168135043884</v>
       </c>
       <c r="P6" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.07930286943495034</v>
+        <v>0.05068152711297184</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05230553290603873</v>
+        <v>0.0316437252144921</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43880</v>
@@ -5640,56 +5121,48 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.08992794834420026</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.09183168135043884</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2457029538737467</v>
+        <v>0.09881409738996361</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>-0.02066180769154664</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.1073124556459222</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.02224473943095457</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.0611783678916169</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -5701,7 +5174,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5732,35 +5205,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43402</v>
+        <v>43458</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43565</v>
+        <v>43578</v>
       </c>
       <c r="M7" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.08992794834420026</v>
+        <v>-0.1692846346126109</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1710223654406263</v>
       </c>
       <c r="P7" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.05068152711297184</v>
+        <v>0.07085501760958975</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.0316437252144921</v>
+        <v>0.0455035633417641</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43880</v>
@@ -5773,40 +5246,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="X7" t="n">
-        <v>-38</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.08992794834420026</v>
+        <v>-0.1692846346126109</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1710223654406263</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="AC7" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.09881409738996361</v>
+        <v>0.2037817544564955</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.02066180769154664</v>
+        <v>-0.006801969564274632</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1073124556459222</v>
+        <v>0.02795576937751154</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>-8</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5826,7 +5299,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5844,52 +5317,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>43402</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43578</v>
+        <v>43545</v>
       </c>
       <c r="M8" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.08992794834420026</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.09183168135043884</v>
       </c>
       <c r="P8" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.07085501760958975</v>
+        <v>0.05065389222244553</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.0455035633417641</v>
+        <v>0.02997933765202255</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43880</v>
@@ -5902,56 +5371,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.08992794834420026</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.09183168135043884</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2037817544564955</v>
+        <v>0.09881409738996361</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.006801969564274632</v>
+        <v>-0.02232619525401618</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02795576937751154</v>
+        <v>0.1073124556459222</v>
       </c>
       <c r="AH8" t="n">
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.01544276986667994</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.03322259851410536</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -5963,7 +5424,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5994,35 +5455,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43402</v>
+        <v>43458</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43545</v>
+        <v>43577</v>
       </c>
       <c r="M9" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.08992794834420026</v>
+        <v>-0.1692846346126109</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1710223654406263</v>
       </c>
       <c r="P9" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.05065389222244553</v>
+        <v>0.069957021893594</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.02997933765202255</v>
+        <v>0.0447727410346011</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43880</v>
@@ -6035,40 +5496,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="X9" t="n">
-        <v>-38</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.08992794834420026</v>
+        <v>-0.1692846346126109</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1710223654406263</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="AC9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.09881409738996361</v>
+        <v>0.2037817544564955</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.02232619525401618</v>
+        <v>-0.007532791871437627</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1073124556459222</v>
+        <v>0.02795576937751154</v>
       </c>
       <c r="AH9" t="n">
-        <v>8</v>
+        <v>-9</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6079,143 +5540,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>43577</v>
-      </c>
-      <c r="M10" t="n">
-        <v>144</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1692846346126109</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1710223654406263</v>
-      </c>
-      <c r="P10" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.069957021893594</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.0447727410346011</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1692846346126109</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1710223654406263</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2037817544564955</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.007532791871437627</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.02795576937751154</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.01471194755951695</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.03322259851410536</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6228,7 +5552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6711,7 +6035,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6721,7 +6045,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6732,13 +6056,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -6747,26 +6075,24 @@
       <c r="K4" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>122</v>
+        <v>473</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="P4" t="n">
-        <v>121</v>
+        <v>473</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1193940004707371</v>
+        <v>0.241160306106721</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0608199262236669</v>
+        <v>0.241160306106721</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>44564</v>
@@ -6775,9 +6101,11 @@
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.2441980324323781</v>
+      </c>
       <c r="W4" t="n">
         <v>23</v>
       </c>
@@ -6785,37 +6113,33 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>44</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4071307910896131</v>
+        <v>0.4615913734580137</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.003078629160440563</v>
+        <v>0.1772617507226135</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.02648023552616652</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -6832,7 +6156,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6863,7 +6187,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -6872,9 +6196,11 @@
       <c r="K5" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>44076</v>
+      </c>
       <c r="M5" t="n">
-        <v>473</v>
+        <v>137</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>-0.3158142431874948</v>
@@ -6883,13 +6209,13 @@
         <v>-0.3158142431874948</v>
       </c>
       <c r="P5" t="n">
-        <v>473</v>
+        <v>136</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.241160306106721</v>
+        <v>0.1374551796547841</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.241160306106721</v>
+        <v>0.07416713144199225</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>44564</v>
@@ -6898,11 +6224,9 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2441980324323781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
         <v>23</v>
       </c>
@@ -6919,24 +6243,28 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>59</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
         <v>0.4615913734580137</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.1772617507226135</v>
+        <v>0.01026857605788478</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -6953,7 +6281,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6971,52 +6299,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43913</v>
+        <v>43993</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>44076</v>
+        <v>43998</v>
       </c>
       <c r="M6" t="n">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.01956263543103032</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.04992556603898302</v>
       </c>
       <c r="P6" t="n">
-        <v>136</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1374551796547841</v>
+        <v>0.008869539401277573</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.07416713144199225</v>
+        <v>0.003711512629312721</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>44564</v>
@@ -7029,58 +6353,54 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.01956263543103032</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.04992556603898302</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="n">
-        <v>59</v>
+        <v>-52</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4615913734580137</v>
+        <v>0.01995296807117364</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.01026857605788478</v>
+        <v>-0.06018704275479474</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.2962516077564645</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>-89</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.01334720521832534</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.02648023552616652</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.03723595092910825</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.03530206183892504</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7090,7 +6410,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7121,35 +6441,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43993</v>
+        <v>43913</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43998</v>
+        <v>44048</v>
       </c>
       <c r="M7" t="n">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.01956263543103032</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.04992556603898302</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.008869539401277573</v>
+        <v>0.1193833987623904</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.003711512629312721</v>
+        <v>0.05956563440545749</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>44564</v>
@@ -7162,40 +6482,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.01956263543103032</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.04992556603898302</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="AC7" t="n">
-        <v>-52</v>
+        <v>39</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.01995296807117364</v>
+        <v>0.4071307910896131</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06018704275479474</v>
+        <v>-0.004332920978649971</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2962516077564645</v>
+        <v>0.02648023552616652</v>
       </c>
       <c r="AH7" t="n">
-        <v>-89</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7208,7 +6528,7 @@
         <v>0.03723595092910825</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.03530206183892504</v>
+        <v>-0.02072738717352474</v>
       </c>
     </row>
     <row r="8">
@@ -7219,7 +6539,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7237,52 +6557,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43913</v>
+        <v>43889</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>44048</v>
+        <v>44075</v>
       </c>
       <c r="M8" t="n">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="P8" t="n">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1193833987623904</v>
+        <v>0.08239599892152345</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05956563440545749</v>
+        <v>0.04429729795846984</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>44564</v>
@@ -7295,62 +6611,50 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="AC8" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4071307910896131</v>
+        <v>0.1542767234392135</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.004332920978649971</v>
+        <v>-0.01960125742563762</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02648023552616652</v>
+        <v>0.1821576248858281</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.001254291818209408</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.03723595092910825</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.02072738717352474</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7360,7 +6664,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7391,35 +6695,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43889</v>
+        <v>43913</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>44075</v>
+        <v>44069</v>
       </c>
       <c r="M9" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="P9" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.08239599892152345</v>
+        <v>0.1281248599920793</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.04429729795846984</v>
+        <v>0.06786878172373392</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>44564</v>
@@ -7432,40 +6736,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="AC9" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1542767234392135</v>
+        <v>0.4324251841864841</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.01960125742563762</v>
+        <v>0.003970226339626459</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1821576248858281</v>
+        <v>0.01393098327254794</v>
       </c>
       <c r="AH9" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -7476,143 +6780,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M10" t="n">
-        <v>132</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="P10" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1281248599920793</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.06786878172373392</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>109</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>54</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.4324251841864841</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.003970226339626459</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.01393098327254794</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.007048855500067022</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.01254925225361858</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7625,7 +6792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8108,7 +7275,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8118,7 +7285,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8129,41 +7296,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>44729</v>
+        <v>44848</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>45317</v>
+        <v>45167</v>
       </c>
       <c r="M4" t="n">
-        <v>518</v>
+        <v>415</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2236029749778981</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2622253758368088</v>
       </c>
       <c r="P4" t="n">
-        <v>517</v>
+        <v>376</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1212946577391739</v>
+        <v>0.1644849879505295</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0986257965760659</v>
+        <v>0.1197396830634786</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>45707</v>
@@ -8176,40 +7347,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="X4" t="n">
-        <v>-80</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2236029749778981</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2622253758368088</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>403</v>
+        <v>218</v>
       </c>
       <c r="AC4" t="n">
-        <v>183</v>
+        <v>-2</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2858663094007141</v>
+        <v>0.2880008137222483</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03076642269399363</v>
+        <v>-0.009652536206580922</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.0644825323318996</v>
+        <v>0.06319373364962577</v>
       </c>
       <c r="AH4" t="n">
-        <v>271</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8218,8 +7389,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.9069015013894919</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.4748825853361665</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8229,7 +7404,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8260,7 +7435,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -8270,25 +7445,25 @@
         <v>44848</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>45167</v>
+        <v>45244</v>
       </c>
       <c r="M5" t="n">
-        <v>415</v>
+        <v>469</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2236029749778981</v>
+        <v>-0.2597539727423155</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2622253758368088</v>
+        <v>-0.2622253758368087</v>
       </c>
       <c r="P5" t="n">
-        <v>376</v>
+        <v>467</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1644849879505295</v>
+        <v>0.155126915081858</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1197396830634786</v>
+        <v>0.1200331647266549</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>45707</v>
@@ -8307,34 +7482,34 @@
         <v>2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2236029749778981</v>
+        <v>-0.2597539727423155</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2622253758368088</v>
+        <v>-0.2622253758368087</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2</v>
+        <v>52</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2880008137222483</v>
+        <v>0.3509022178809931</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.009652536206580922</v>
+        <v>-0.009359054543404619</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.06319373364962577</v>
+        <v>0.02704273588520834</v>
       </c>
       <c r="AH5" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8347,7 +7522,7 @@
         <v>0.9069015013894919</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.4748825853361665</v>
+        <v>-0.1655269949776802</v>
       </c>
     </row>
     <row r="6">
@@ -8358,7 +7533,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8376,52 +7551,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>44848</v>
+        <v>44588</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45244</v>
+        <v>45019</v>
       </c>
       <c r="M6" t="n">
-        <v>469</v>
+        <v>313</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2597539727423155</v>
+        <v>-0.1254104153489787</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.2622253758368087</v>
+        <v>-0.1254104153489787</v>
       </c>
       <c r="P6" t="n">
-        <v>467</v>
+        <v>312</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.155126915081858</v>
+        <v>0.07284139588447486</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1200331647266549</v>
+        <v>0.04606894378819115</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>45707</v>
@@ -8434,61 +7605,53 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>197</v>
+        <v>17</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>-178</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2597539727423155</v>
+        <v>-0.1254104153489787</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2622253758368087</v>
+        <v>-0.1254104153489787</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="AC6" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3509022178809931</v>
+        <v>0.1433934471092746</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.009359054543404619</v>
+        <v>-0.08332327548186838</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02704273588520834</v>
+        <v>0.1613862932785451</v>
       </c>
       <c r="AH6" t="n">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.02140736815058901</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.03743979644669126</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-131</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="n">
-        <v>0.9069015013894919</v>
+        <v>0.05128529554140782</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.1655269949776802</v>
+        <v>-0.04968647066593979</v>
       </c>
     </row>
     <row r="7">
@@ -8499,7 +7662,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8530,35 +7693,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>44588</v>
+        <v>44729</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45019</v>
+        <v>45090</v>
       </c>
       <c r="M7" t="n">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.2504502125606831</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.2504502125606831</v>
       </c>
       <c r="P7" t="n">
-        <v>312</v>
+        <v>361</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.07284139588447486</v>
+        <v>0.1595473300416926</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.04606894378819115</v>
+        <v>0.1084945755197246</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>45707</v>
@@ -8571,40 +7734,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="X7" t="n">
-        <v>-178</v>
+        <v>-80</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.2504502125606831</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.2504502125606831</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="AC7" t="n">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1433934471092746</v>
+        <v>0.3341341919611436</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.08332327548186838</v>
+        <v>-0.02089764375033494</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1613862932785451</v>
+        <v>0.03634649606684071</v>
       </c>
       <c r="AH7" t="n">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8617,7 +7780,7 @@
         <v>0.05128529554140782</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.04968647066593979</v>
+        <v>0.006526314267764954</v>
       </c>
     </row>
     <row r="8">
@@ -8628,7 +7791,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8646,52 +7809,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>44729</v>
+        <v>44995</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>45090</v>
+        <v>45006</v>
       </c>
       <c r="M8" t="n">
-        <v>362</v>
+        <v>304</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.06055724913043437</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.1037854592728726</v>
       </c>
       <c r="P8" t="n">
-        <v>361</v>
+        <v>139</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1595473300416926</v>
+        <v>0.05059978400514363</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1084945755197246</v>
+        <v>0.03154014998847552</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>45707</v>
@@ -8704,61 +7863,53 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>115</v>
+        <v>297</v>
       </c>
       <c r="X8" t="n">
-        <v>-80</v>
+        <v>102</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.06055724913043437</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.1037854592728726</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>247</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>27</v>
+        <v>-213</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3341341919611436</v>
+        <v>0.06446081900614109</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02089764375033494</v>
+        <v>-0.09785206928158402</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.03634649606684071</v>
+        <v>0.2262394594970895</v>
       </c>
       <c r="AH8" t="n">
-        <v>115</v>
+        <v>-125</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.009868778943658688</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.02813603626505889</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-156</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
         <v>0.05128529554140782</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.006526314267764954</v>
+        <v>-0.04873520817013055</v>
       </c>
     </row>
     <row r="9">
@@ -8769,7 +7920,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8800,35 +7951,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>44995</v>
+        <v>44846</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>45006</v>
+        <v>45079</v>
       </c>
       <c r="M9" t="n">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.06055724913043437</v>
+        <v>-0.231288305099722</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1037854592728726</v>
+        <v>-0.231288305099722</v>
       </c>
       <c r="P9" t="n">
-        <v>139</v>
+        <v>354</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.05059978400514363</v>
+        <v>0.1382702215519126</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.03154014998847552</v>
+        <v>0.09311482455886631</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>45707</v>
@@ -8841,40 +7992,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="X9" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.06055724913043437</v>
+        <v>-0.231288305099722</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1037854592728726</v>
+        <v>-0.231288305099722</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>160</v>
       </c>
       <c r="AC9" t="n">
-        <v>-213</v>
+        <v>-60</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.06446081900614109</v>
+        <v>0.3008778279738884</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.09785206928158402</v>
+        <v>-0.03627739471119322</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2262394594970895</v>
+        <v>0.05550840352780184</v>
       </c>
       <c r="AH9" t="n">
-        <v>-125</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8887,147 +8038,6 @@
         <v>0.05128529554140782</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.04873520817013055</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45079</v>
-      </c>
-      <c r="M10" t="n">
-        <v>355</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.231288305099722</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.231288305099722</v>
-      </c>
-      <c r="P10" t="n">
-        <v>354</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1382702215519126</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09311482455886631</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>195</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.231288305099722</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.231288305099722</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.3008778279738884</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.03627739471119322</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.05550840352780184</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>-0.005510972017199592</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.008974128804097758</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-243</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.05128529554140782</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>0.007178166975881028</v>
       </c>
     </row>
@@ -9042,7 +8052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9525,7 +8535,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9535,7 +8545,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9546,87 +8556,87 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45917</v>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.06321320299387231</v>
+        <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05173160794390522</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>56</v>
+        <v>-55</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1374994254296262</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.009320946886891092</v>
+        <v>-0.06105255483079631</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.0710886759431909</v>
+        <v>0.1919673527633516</v>
       </c>
       <c r="AH4" t="n">
-        <v>41</v>
+        <v>-70</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9635,8 +8645,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.2134223460531468</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1592570553973541</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9646,7 +8660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9677,77 +8691,81 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45917</v>
+      </c>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.06321320299387231</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>0.05173160794390522</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>56</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.1374994254296262</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.06105255483079631</v>
+        <v>-0.009320946886891092</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1919673527633516</v>
+        <v>0.0710886759431909</v>
       </c>
       <c r="AH5" t="n">
-        <v>-70</v>
+        <v>41</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9760,7 +8778,7 @@
         <v>0.2134223460531468</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1592570553973541</v>
+        <v>-0.1114588698733576</v>
       </c>
     </row>
     <row r="6">
@@ -9771,7 +8789,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9789,52 +8807,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>45755</v>
+        <v>45719</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45917</v>
+        <v>45811</v>
       </c>
       <c r="M6" t="n">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.06793604487478933</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.06793604487478933</v>
       </c>
       <c r="P6" t="n">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.06321320299387231</v>
+        <v>0.054826076669319</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05173160794390522</v>
+        <v>0.03172636763019378</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>46021</v>
@@ -9847,62 +8861,50 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.06793604487478933</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.06793604487478933</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="AC6" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1374994254296262</v>
+        <v>0.07288775035363648</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.009320946886891092</v>
+        <v>-0.02932618720060253</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.0710886759431909</v>
+        <v>0.1240313078885623</v>
       </c>
       <c r="AH6" t="n">
-        <v>41</v>
+        <v>-6</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.2134223460531468</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.1114588698733576</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9912,7 +8914,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9943,35 +8945,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>45719</v>
+        <v>45755</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45811</v>
+        <v>45862</v>
       </c>
       <c r="M7" t="n">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.06793604487478933</v>
+        <v>-0.164302162285406</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.06793604487478933</v>
+        <v>-0.164302162285406</v>
       </c>
       <c r="P7" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.054826076669319</v>
+        <v>0.08288297327417904</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.03172636763019378</v>
+        <v>0.05833765303150832</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>46021</v>
@@ -9984,40 +8986,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="X7" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.06793604487478933</v>
+        <v>-0.164302162285406</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.06793604487478933</v>
+        <v>-0.164302162285406</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.07288775035363648</v>
+        <v>0.1966047473985664</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.02932618720060253</v>
+        <v>-0.002714901799287989</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1240313078885623</v>
+        <v>0.02766519047794569</v>
       </c>
       <c r="AH7" t="n">
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -10037,7 +9039,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10055,52 +9057,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>45755</v>
+        <v>45729</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>45862</v>
+        <v>45910</v>
       </c>
       <c r="M8" t="n">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.1267516996503394</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.1267516996503394</v>
       </c>
       <c r="P8" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.08288297327417904</v>
+        <v>0.08846503518656774</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05833765303150832</v>
+        <v>0.07114640563329215</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>46021</v>
@@ -10113,56 +9111,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.1267516996503394</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.164302162285406</v>
+        <v>-0.1267516996503394</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="AC8" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1966047473985664</v>
+        <v>0.1451496665949263</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.002714901799287989</v>
+        <v>0.01009385080249584</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02766519047794569</v>
+        <v>0.06521565311301225</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.006606045087603103</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.04342348546524522</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-38</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -10174,7 +9164,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10205,35 +9195,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>45729</v>
+        <v>45755</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>45910</v>
+        <v>45939</v>
       </c>
       <c r="M9" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1267516996503394</v>
+        <v>-0.1847093048502678</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1267516996503394</v>
+        <v>-0.1847093048502678</v>
       </c>
       <c r="P9" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.08846503518656774</v>
+        <v>0.1033674131889683</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.07114640563329215</v>
+        <v>0.08910722284893841</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>46021</v>
@@ -10246,40 +9236,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="X9" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1267516996503394</v>
+        <v>-0.1847093048502678</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1267516996503394</v>
+        <v>-0.1847093048502678</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="AC9" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1451496665949263</v>
+        <v>0.2265563754733457</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.01009385080249584</v>
+        <v>0.0280546680181421</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.06521565311301225</v>
+        <v>0.00725804791308382</v>
       </c>
       <c r="AH9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10290,143 +9280,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45939</v>
-      </c>
-      <c r="M10" t="n">
-        <v>161</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1847093048502678</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1847093048502678</v>
-      </c>
-      <c r="P10" t="n">
-        <v>160</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1033674131889683</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.08910722284893841</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>34</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1847093048502678</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1847093048502678</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>127</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>72</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2265563754733457</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.0280546680181421</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.00725804791308382</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>57</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.03737561490503319</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.06383062803010708</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.176694263222226</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1048,51 +1049,51 @@
         <v>0.7041511784725716</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1197,51 +1198,51 @@
         <v>0.7793754420589409</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1346,51 +1347,51 @@
         <v>1.563297100944838</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -1495,51 +1496,51 @@
         <v>1.243912963630532</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1644,11 +1645,11 @@
         <v>0.2642635252451979</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
@@ -1656,23 +1657,23 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
@@ -1680,15 +1681,15 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr"/>
@@ -1793,35 +1794,35 @@
         <v>0.8766066201280511</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1829,15 +1830,15 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -2142,66 +2143,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.0903200482301444</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.04076898034342899</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582909292</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493482</v>
+        <v>0.2044255219913533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2249,66 +2252,68 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>36118</v>
+      </c>
       <c r="M3" t="n">
-        <v>1896</v>
+        <v>88</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.5351953756562349</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.5405877541480402</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="P3" t="n">
-        <v>1893</v>
+        <v>86</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.3318786120147709</v>
+        <v>0.08971493195499394</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.3318786120147709</v>
+        <v>0.04095866547233682</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>-0.07379561685859526</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5351953756562349</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.5405877541480402</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.151441589919315</v>
+        <v>0.2058228721729791</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2316,9 +2321,11 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -2370,34 +2377,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>36811</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38415</v>
+        <v>36510</v>
       </c>
       <c r="M4" t="n">
-        <v>1242</v>
+        <v>358</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2117116495671395</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.22085688806862</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="P4" t="n">
-        <v>1238</v>
+        <v>356</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1407604164514403</v>
+        <v>0.1049145638682134</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.1139416336580026</v>
+        <v>0.09619866970316232</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2407,39 +2414,43 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>141</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-497</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2117116495671395</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.22085688806862</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1101</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>272</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2685713285638252</v>
+        <v>0.2058228721729791</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.2179369783567683</v>
+        <v>0.0552400042308255</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3234837260890954</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>270</v>
+      </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -2491,34 +2502,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>38986</v>
+        <v>36104</v>
       </c>
       <c r="M5" t="n">
-        <v>1636</v>
+        <v>78</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.4314086080914217</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.4380050570761586</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="P5" t="n">
-        <v>1632</v>
+        <v>76</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2204505869030779</v>
+        <v>0.09244184339539407</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.2047867876822711</v>
+        <v>0.03976199856961407</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2528,39 +2539,43 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.4314086080914217</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.4380050570761586</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1053</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.7587322183041179</v>
+        <v>0.2058228721729791</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1270918243324998</v>
+        <v>-0.00119666690272275</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1037867675648132</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-10</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -2612,76 +2627,80 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37664</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>36152</v>
+      </c>
       <c r="M6" t="n">
-        <v>1896</v>
+        <v>111</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.605298363987808</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.6098774505571757</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="P6" t="n">
-        <v>1893</v>
+        <v>109</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.430410363505689</v>
+        <v>0.09663549346813932</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.430410363505689</v>
+        <v>0.04949162829774523</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-0.3180149709140817</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>724</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.605298363987808</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.6098774505571757</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1172</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>25</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>1.533559298368631</v>
+        <v>0.2058228721729791</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.09853175149091803</v>
+        <v>0.008532962825408413</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.07010298833157314</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23</v>
+      </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -2733,76 +2752,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36105</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>79</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.5491190720288466</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.5543499163256078</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="P7" t="n">
-        <v>1893</v>
+        <v>77</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3461930634419392</v>
+        <v>0.09189905978075769</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3461930634419392</v>
+        <v>0.03977792495871341</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.113651832784307</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.5491190720288466</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.5543499163256078</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.217880460146627</v>
+        <v>0.2058228721729791</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.01431445142716825</v>
+        <v>-0.001180740513623407</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.0139236963726117</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-9</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -2854,86 +2877,86 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>37375</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>38232</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>1116</v>
+        <v>90</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1607561803938017</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1911504799548355</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1004</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1241029990867884</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.09523030997169735</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-114</v>
+        <v>-31</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1607561803938017</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1911504799548355</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>592</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1915488403229872</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.2366483020430736</v>
+        <v>-0.04095866547233682</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.3744391952624332</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>0.1706908012136737</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-57</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
-        <v>0.08270819824638442</v>
+        <v>0.1034278830282558</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-0.06916594252835273</v>
+        <v>-0.08435133805704931</v>
       </c>
     </row>
     <row r="9">
@@ -2979,34 +3002,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>38924</v>
+        <v>36102</v>
       </c>
       <c r="M9" t="n">
-        <v>1593</v>
+        <v>76</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.3899810452148498</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4341707534324699</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="P9" t="n">
-        <v>1475</v>
+        <v>75</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2147873729662626</v>
+        <v>0.08522521481650464</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1968879963369338</v>
+        <v>0.03619091219269772</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -3016,49 +3039,53 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X9" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3899810452148498</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4341707534324699</v>
+        <v>-0.1581346033647496</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1010</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-10</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.6392933238479479</v>
+        <v>0.187838345650954</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1349906156778372</v>
+        <v>-0.004767753279639096</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1452143304413851</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.01255619784892414</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-12</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>0.08270819824638442</v>
+        <v>0.1034278830282558</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.1361240023967677</v>
+        <v>-0.03985989506857002</v>
       </c>
     </row>
   </sheetData>
@@ -3356,68 +3383,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.503509252857314</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2352416489517779</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1561727120528913</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459927</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616547</v>
+        <v>0.9463998245842122</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3465,68 +3490,66 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.5364587231151221</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.5405877541480402</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1894</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.331966121208649</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.331966121208649</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>40568</v>
-      </c>
-      <c r="M3" t="n">
-        <v>830</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.4375057689528339</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.4456113326384448</v>
-      </c>
-      <c r="P3" t="n">
-        <v>816</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2093201856322416</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1148777108501162</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>-0.07631305728962323</v>
+      </c>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4375057689528339</v>
+        <v>-0.5364587231151221</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4456113326384448</v>
+        <v>-0.5405877541480402</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>475</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-385</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.7777960107045938</v>
+        <v>1.157305184816051</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3534,11 +3557,9 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -3590,34 +3611,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>36811</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38677</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1423</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2138542317021509</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.22085688806862</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1421</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1325252033674012</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1148508748014063</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>40765</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40784</v>
-      </c>
-      <c r="M4" t="n">
-        <v>980</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.07135481844085556</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1227419066313019</v>
-      </c>
-      <c r="P4" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.01516685097673147</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.009043865044496601</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3627,54 +3648,46 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>967</v>
+        <v>140</v>
       </c>
       <c r="X4" t="n">
-        <v>612</v>
+        <v>-497</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.07135481844085556</v>
+        <v>-0.2138542317021509</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.22085688806862</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-847</v>
-      </c>
+        <v>1283</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.07683754770692364</v>
+        <v>0.2720287258750815</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1058338458056196</v>
+        <v>-0.2171152464072427</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3661509505119783</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-462</v>
-      </c>
+        <v>0.3226044914129712</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.1461342146462365</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.1068371958786292</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3719,34 +3732,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>38988</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1637</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.4329540498802742</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.4380050570761584</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1635</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2203834950785044</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.2048409816910139</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>40533</v>
-      </c>
-      <c r="M5" t="n">
-        <v>807</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3743492138682257</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3744774130256878</v>
-      </c>
-      <c r="P5" t="n">
-        <v>805</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1546755474705558</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.08370501759350023</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -3756,54 +3769,46 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.4329540498802742</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.4380050570761584</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>452</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-408</v>
-      </c>
+        <v>1055</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.5983357204467421</v>
+        <v>0.763525512859867</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.03117269325661598</v>
+        <v>-0.1271251395176351</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.06315655508460816</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-23</v>
-      </c>
+        <v>0.1035046732348479</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1461342146462365</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.007149815379016156</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3848,80 +3853,76 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37664</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.6063711702439391</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.6098774505571758</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1894</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.4305238533859753</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.4305238533859753</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>40004</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40399</v>
-      </c>
-      <c r="M6" t="n">
-        <v>713</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2064790741024939</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2161164061045036</v>
-      </c>
-      <c r="P6" t="n">
-        <v>705</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1080257419379396</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.05495415235536932</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.3198686186799816</v>
+      </c>
       <c r="W6" t="n">
-        <v>441</v>
+        <v>723</v>
       </c>
       <c r="X6" t="n">
         <v>86</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2064790741024939</v>
+        <v>-0.6063711702439391</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2161164061045036</v>
+        <v>-0.6098774505571758</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>272</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-588</v>
-      </c>
+        <v>1172</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2602062117882489</v>
+        <v>1.540464326811932</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.05992355849474688</v>
+        <v>0.09855773217732633</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.23102669485034</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-203</v>
-      </c>
+        <v>-0.06991244712881695</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -3973,80 +3974,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.5503445746266686</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.5543499163256078</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1894</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.346284347046279</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.346284347046279</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40462</v>
-      </c>
-      <c r="M7" t="n">
-        <v>757</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3609757233342479</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3687366895678811</v>
-      </c>
-      <c r="P7" t="n">
-        <v>749</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1580972654520925</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.08286728510719067</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.1160609432924526</v>
+      </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3609757233342479</v>
+        <v>-0.5503445746266686</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3687366895678811</v>
+        <v>-0.5543499163256078</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>402</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-458</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.5648857743209961</v>
+        <v>1.223925129269237</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.03201042574292554</v>
+        <v>0.01431822583763004</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.07653004561858601</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-73</v>
-      </c>
+        <v>-0.01388585151154653</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4098,34 +4095,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37375</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>38232</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1115</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1609469119758051</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1911504799548355</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1004</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1241585883388871</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.09525542013956202</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>40416</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>40486</v>
-      </c>
-      <c r="M8" t="n">
-        <v>775</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1513517485327929</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1616586033180829</v>
-      </c>
-      <c r="P8" t="n">
-        <v>767</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.0874086978492416</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04635639564767428</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -4135,50 +4132,50 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>726</v>
+        <v>523</v>
       </c>
       <c r="X8" t="n">
-        <v>371</v>
+        <v>-114</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1513517485327929</v>
+        <v>-0.1609469119758051</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1616586033180829</v>
+        <v>-0.1911504799548355</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>49</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-811</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1783445005290762</v>
+        <v>0.1918197004134785</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.06852131520244192</v>
+        <v>-0.236710701069087</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.286154020420041</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-426</v>
-      </c>
+        <v>0.375511811139317</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.08565903934550501</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.07148494660096649</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4223,34 +4220,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>38924</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1592</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.3886139835742487</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.4341707534324698</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1472</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.2148547024638794</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.1969398418384406</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40466</v>
-      </c>
-      <c r="M9" t="n">
-        <v>761</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3723569839339402</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3799797244656153</v>
-      </c>
-      <c r="P9" t="n">
-        <v>753</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1635517543216592</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.08595216934937883</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4260,50 +4257,50 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3723569839339402</v>
+        <v>-0.3886139835742487</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3799797244656153</v>
+        <v>-0.4341707534324698</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>406</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-454</v>
-      </c>
+        <v>1010</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.5932623711290519</v>
+        <v>0.6356278572515295</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.02892554150073738</v>
+        <v>-0.1350262793702084</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.06514878501889365</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-69</v>
-      </c>
+        <v>0.1478447395408734</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.08565903934550501</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.1403984132052861</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4600,34 +4597,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856417</v>
+        <v>0.2352416489517779</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.0521896337568788</v>
+        <v>0.1562010221613542</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -4637,22 +4634,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -4661,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160741</v>
+        <v>1.014136226616547</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -4709,34 +4706,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43588</v>
+        <v>40568</v>
       </c>
       <c r="M3" t="n">
-        <v>153</v>
+        <v>830</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.4375057689528339</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.4456113326384448</v>
       </c>
       <c r="P3" t="n">
-        <v>148</v>
+        <v>816</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.07930286943495034</v>
+        <v>0.2093201856322416</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.05230553290603873</v>
+        <v>0.1148985352336554</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -4746,31 +4743,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.4375057689528339</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.4456113326384448</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>89</v>
+        <v>475</v>
       </c>
       <c r="AC3" t="n">
-        <v>13</v>
+        <v>-385</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2457029538737467</v>
+        <v>0.7777960107045938</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -4834,34 +4831,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>40765</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43588</v>
+        <v>40784</v>
       </c>
       <c r="M4" t="n">
-        <v>153</v>
+        <v>980</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.07135481844085556</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="P4" t="n">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.07930286943495034</v>
+        <v>0.01516685097673147</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05230553290603873</v>
+        <v>0.009045504465346558</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -4871,40 +4868,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>967</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.07135481844085556</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.1227419066313019</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>13</v>
+        <v>-847</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2457029538737467</v>
+        <v>0.07683754770692364</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0</v>
+        <v>-0.1058530307683088</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0</v>
+        <v>0.3661509505119783</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-462</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4913,8 +4910,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1461342146462365</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1068371958786292</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4959,34 +4960,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43588</v>
+        <v>40533</v>
       </c>
       <c r="M5" t="n">
-        <v>153</v>
+        <v>807</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="P5" t="n">
-        <v>148</v>
+        <v>805</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.07930286943495034</v>
+        <v>0.1546755474705558</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.05230553290603873</v>
+        <v>0.08372019116701263</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4996,40 +4997,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>89</v>
+        <v>452</v>
       </c>
       <c r="AC5" t="n">
-        <v>13</v>
+        <v>-408</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2457029538737467</v>
+        <v>0.5983357204467421</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0</v>
+        <v>-0.03117834406664274</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>0.06315655508460816</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5038,8 +5039,12 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1461342146462365</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.007149815379016156</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5084,34 +5089,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43402</v>
+        <v>40004</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43565</v>
+        <v>40399</v>
       </c>
       <c r="M6" t="n">
-        <v>137</v>
+        <v>713</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.08992794834420026</v>
+        <v>-0.2064790741024939</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.2161164061045036</v>
       </c>
       <c r="P6" t="n">
-        <v>132</v>
+        <v>705</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.05068152711297184</v>
+        <v>0.1080257419379396</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.0316437252144921</v>
+        <v>0.05496411413417958</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5121,40 +5126,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>26</v>
+        <v>441</v>
       </c>
       <c r="X6" t="n">
-        <v>-38</v>
+        <v>86</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.08992794834420026</v>
+        <v>-0.2064790741024939</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.2161164061045036</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>111</v>
+        <v>272</v>
       </c>
       <c r="AC6" t="n">
-        <v>35</v>
+        <v>-588</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.09881409738996361</v>
+        <v>0.2602062117882489</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.02066180769154664</v>
+        <v>-0.05993442109947579</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1073124556459222</v>
+        <v>0.23102669485034</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>-203</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -5209,34 +5214,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43578</v>
+        <v>40462</v>
       </c>
       <c r="M7" t="n">
-        <v>145</v>
+        <v>757</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.3609757233342479</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.3687366895678811</v>
       </c>
       <c r="P7" t="n">
-        <v>140</v>
+        <v>749</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.07085501760958975</v>
+        <v>0.1580972654520925</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.0455035633417641</v>
+        <v>0.08288230682128256</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5246,40 +5251,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.3609757233342479</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.3687366895678811</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>81</v>
+        <v>402</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>-458</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2037817544564955</v>
+        <v>0.5648857743209961</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.006801969564274632</v>
+        <v>-0.03201622841237281</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.02795576937751154</v>
+        <v>0.07653004561858601</v>
       </c>
       <c r="AH7" t="n">
-        <v>-8</v>
+        <v>-73</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5334,34 +5339,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43402</v>
+        <v>40416</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43545</v>
+        <v>40486</v>
       </c>
       <c r="M8" t="n">
-        <v>123</v>
+        <v>775</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.08992794834420026</v>
+        <v>-0.1513517485327929</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1616586033180829</v>
       </c>
       <c r="P8" t="n">
-        <v>118</v>
+        <v>767</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.05065389222244553</v>
+        <v>0.0874086978492416</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.02997933765202255</v>
+        <v>0.04636479887363793</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5371,40 +5376,40 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>26</v>
+        <v>726</v>
       </c>
       <c r="X8" t="n">
-        <v>-38</v>
+        <v>371</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.08992794834420026</v>
+        <v>-0.1513517485327929</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.09183168135043884</v>
+        <v>-0.1616586033180829</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="AC8" t="n">
-        <v>21</v>
+        <v>-811</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.09881409738996361</v>
+        <v>0.1783445005290762</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02232619525401618</v>
+        <v>-0.06853373636001744</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1073124556459222</v>
+        <v>0.286154020420041</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>-426</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -5459,34 +5464,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43577</v>
+        <v>40466</v>
       </c>
       <c r="M9" t="n">
-        <v>144</v>
+        <v>761</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.3723569839339402</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.3799797244656153</v>
       </c>
       <c r="P9" t="n">
-        <v>139</v>
+        <v>753</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.069957021893594</v>
+        <v>0.1635517543216592</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.0447727410346011</v>
+        <v>0.0859677502738881</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -5496,40 +5501,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1692846346126109</v>
+        <v>-0.3723569839339402</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1710223654406263</v>
+        <v>-0.3799797244656153</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>80</v>
+        <v>406</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>-454</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2037817544564955</v>
+        <v>0.5932623711290519</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.007532791871437627</v>
+        <v>-0.02893078495976727</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.02795576937751154</v>
+        <v>0.06514878501889365</v>
       </c>
       <c r="AH9" t="n">
-        <v>-9</v>
+        <v>-69</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -5836,34 +5841,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606706</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860074</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428352</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049091</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5873,22 +5878,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5897,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986547</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5945,34 +5950,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43636</v>
+      </c>
+      <c r="M3" t="n">
+        <v>187</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1991277646524821</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1991277646524821</v>
+      </c>
+      <c r="P3" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.07312544540501786</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05321490270851575</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44046</v>
-      </c>
-      <c r="M3" t="n">
-        <v>115</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3158142431874948</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3158142431874948</v>
-      </c>
-      <c r="P3" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1291668938515992</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06389855538410746</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5982,31 +5987,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="AC3" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4615913734580137</v>
+        <v>0.2486386165779311</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6070,76 +6075,80 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43636</v>
+      </c>
+      <c r="M4" t="n">
+        <v>187</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1991277646524821</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1991277646524821</v>
+      </c>
+      <c r="P4" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.07312544540501786</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05321490270851575</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>473</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.3158142431874948</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.3158142431874948</v>
-      </c>
-      <c r="P4" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.241160306106721</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.241160306106721</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>-0.2441980324323781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>44</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4615913734580137</v>
+        <v>0.2486386165779311</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.1772617507226135</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -6191,34 +6200,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43636</v>
+      </c>
+      <c r="M5" t="n">
+        <v>187</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1991277646524821</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1991277646524821</v>
+      </c>
+      <c r="P5" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.07312544540501786</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.05321490270851575</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44076</v>
-      </c>
-      <c r="M5" t="n">
-        <v>137</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3158142431874948</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3158142431874948</v>
-      </c>
-      <c r="P5" t="n">
-        <v>136</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1374551796547841</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.07416713144199225</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6228,40 +6237,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="AC5" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4615913734580137</v>
+        <v>0.2486386165779311</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.01026857605788478</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -6316,34 +6325,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43402</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43573</v>
+      </c>
+      <c r="M6" t="n">
+        <v>144</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.09206761032861699</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.09206761032861699</v>
+      </c>
+      <c r="P6" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.04968101968995928</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.03175121330843278</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43993</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>43998</v>
-      </c>
-      <c r="M6" t="n">
-        <v>82</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.01956263543103032</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.04992556603898302</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.008869539401277573</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.003711512629312721</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -6353,40 +6362,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="X6" t="n">
-        <v>56</v>
+        <v>-38</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.01956263543103032</v>
+        <v>-0.09206761032861699</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.04992556603898302</v>
+        <v>-0.09206761032861699</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="AC6" t="n">
-        <v>-52</v>
+        <v>39</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.01995296807117364</v>
+        <v>0.1014035972017036</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.06018704275479474</v>
+        <v>-0.02146368940008297</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.2962516077564645</v>
+        <v>0.1070601543238651</v>
       </c>
       <c r="AH6" t="n">
-        <v>-89</v>
+        <v>-5</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -6395,12 +6404,8 @@
       <c r="AK6" s="3" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" s="3" t="n">
-        <v>0.03723595092910825</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.03530206183892504</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6445,34 +6450,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="M7" t="n">
+        <v>146</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1712377218258225</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1712377218258225</v>
+      </c>
+      <c r="P7" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.07082321100460236</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.04557431018690544</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44048</v>
-      </c>
-      <c r="M7" t="n">
-        <v>117</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2893340076613283</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2893340076613283</v>
-      </c>
-      <c r="P7" t="n">
-        <v>116</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1193833987623904</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.05956563440545749</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -6482,40 +6487,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AC7" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4071307910896131</v>
+        <v>0.2066186243455379</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.004332920978649971</v>
+        <v>-0.007640592521610312</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.02648023552616652</v>
+        <v>0.02789004282665952</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>-41</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -6524,12 +6529,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.03723595092910825</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.02072738717352474</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6574,34 +6575,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43402</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43545</v>
+      </c>
+      <c r="M8" t="n">
+        <v>124</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.09206761032861699</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.09206761032861699</v>
+      </c>
+      <c r="P8" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05068234814486538</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.03007444058626075</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43889</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44075</v>
-      </c>
-      <c r="M8" t="n">
-        <v>136</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1336566183016668</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1336566183016668</v>
-      </c>
-      <c r="P8" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.08239599892152345</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04429729795846984</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -6611,40 +6612,40 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="X8" t="n">
-        <v>-16</v>
+        <v>-38</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.09206761032861699</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1336566183016668</v>
+        <v>-0.09206761032861699</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="AC8" t="n">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1542767234392135</v>
+        <v>0.1014035972017036</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.01960125742563762</v>
+        <v>-0.023140462122255</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1821576248858281</v>
+        <v>0.1070601543238651</v>
       </c>
       <c r="AH8" t="n">
-        <v>37</v>
+        <v>-25</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -6699,34 +6700,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="M9" t="n">
+        <v>145</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1712377218258225</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1712377218258225</v>
+      </c>
+      <c r="P9" t="n">
+        <v>144</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.069924333199677</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.04484257931667743</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>44069</v>
-      </c>
-      <c r="M9" t="n">
-        <v>132</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3018832599149469</v>
-      </c>
-      <c r="P9" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1281248599920793</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.06786878172373392</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6736,40 +6737,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3018832599149469</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3018832599149469</v>
+        <v>-0.1712377218258225</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="AC9" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4324251841864841</v>
+        <v>0.2066186243455379</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.003970226339626459</v>
+        <v>-0.00837232339183832</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.01393098327254794</v>
+        <v>0.02789004282665952</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>-42</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -7076,34 +7077,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7113,22 +7114,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7137,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088524</v>
+        <v>0.4088864968986547</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7185,34 +7186,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44046</v>
+      </c>
+      <c r="M3" t="n">
+        <v>115</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3158142431874948</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3158142431874948</v>
+      </c>
+      <c r="P3" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1291668938515992</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06389855538410746</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45125</v>
-      </c>
-      <c r="M3" t="n">
-        <v>385</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2867967086275238</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2867967086275238</v>
-      </c>
-      <c r="P3" t="n">
-        <v>384</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1845225032964088</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1293922192700595</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -7222,31 +7223,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2867967086275238</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2867967086275238</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="AC3" t="n">
-        <v>-88</v>
+        <v>37</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4021247687677061</v>
+        <v>0.4615913734580137</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -7310,91 +7311,83 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>473</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.3158142431874948</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3158142431874948</v>
+      </c>
+      <c r="P4" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.241160306106721</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.241160306106721</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45167</v>
-      </c>
-      <c r="M4" t="n">
-        <v>415</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2236029749778981</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2622253758368088</v>
-      </c>
-      <c r="P4" t="n">
-        <v>376</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1644849879505295</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1197396830634786</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.2441980324323781</v>
+      </c>
       <c r="W4" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2236029749778981</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2622253758368088</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>218</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-2</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2880008137222483</v>
+        <v>0.4615913734580137</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.009652536206580922</v>
+        <v>0.1772617507226135</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.06319373364962577</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>86</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.9069015013894919</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.4748825853361665</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7439,34 +7432,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44076</v>
+      </c>
+      <c r="M5" t="n">
+        <v>137</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3158142431874948</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3158142431874948</v>
+      </c>
+      <c r="P5" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1374551796547841</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.07416713144199225</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45244</v>
-      </c>
-      <c r="M5" t="n">
-        <v>469</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2597539727423155</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2622253758368087</v>
-      </c>
-      <c r="P5" t="n">
-        <v>467</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.155126915081858</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1200331647266549</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -7476,40 +7469,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2597539727423155</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2622253758368087</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>272</v>
+        <v>114</v>
       </c>
       <c r="AC5" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.3509022178809931</v>
+        <v>0.4615913734580137</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.009359054543404619</v>
+        <v>0.01026857605788478</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.02704273588520834</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -7518,12 +7511,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.9069015013894919</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.1655269949776802</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7568,34 +7557,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43993</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43998</v>
+      </c>
+      <c r="M6" t="n">
+        <v>82</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.01956263543103032</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.04992556603898302</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.008869539401277573</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.003711512629312721</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44588</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45019</v>
-      </c>
-      <c r="M6" t="n">
-        <v>313</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1254104153489787</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1254104153489787</v>
-      </c>
-      <c r="P6" t="n">
-        <v>312</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.07284139588447486</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.04606894378819115</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7605,40 +7594,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="X6" t="n">
-        <v>-178</v>
+        <v>56</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.01956263543103032</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1254104153489787</v>
+        <v>-0.04992556603898302</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>296</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="n">
-        <v>76</v>
+        <v>-52</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1433934471092746</v>
+        <v>0.01995296807117364</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.08332327548186838</v>
+        <v>-0.06018704275479474</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1613862932785451</v>
+        <v>0.2962516077564645</v>
       </c>
       <c r="AH6" t="n">
-        <v>164</v>
+        <v>-89</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -7648,10 +7637,10 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="n">
-        <v>0.05128529554140782</v>
+        <v>0.03723595092910825</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.04968647066593979</v>
+        <v>-0.03530206183892504</v>
       </c>
     </row>
     <row r="7">
@@ -7697,34 +7686,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44048</v>
+      </c>
+      <c r="M7" t="n">
+        <v>117</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2893340076613283</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2893340076613283</v>
+      </c>
+      <c r="P7" t="n">
+        <v>116</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1193833987623904</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05956563440545749</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45090</v>
-      </c>
-      <c r="M7" t="n">
-        <v>362</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2504502125606831</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2504502125606831</v>
-      </c>
-      <c r="P7" t="n">
-        <v>361</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1595473300416926</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1084945755197246</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7734,40 +7723,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2504502125606831</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>247</v>
+        <v>94</v>
       </c>
       <c r="AC7" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3341341919611436</v>
+        <v>0.4071307910896131</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.02089764375033494</v>
+        <v>-0.004332920978649971</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.03634649606684071</v>
+        <v>0.02648023552616652</v>
       </c>
       <c r="AH7" t="n">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7777,10 +7766,10 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" s="3" t="n">
-        <v>0.05128529554140782</v>
+        <v>0.03723595092910825</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>0.006526314267764954</v>
+        <v>-0.02072738717352474</v>
       </c>
     </row>
     <row r="8">
@@ -7826,34 +7815,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43889</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44075</v>
+      </c>
+      <c r="M8" t="n">
+        <v>136</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1336566183016668</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1336566183016668</v>
+      </c>
+      <c r="P8" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.08239599892152345</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04429729795846984</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45006</v>
-      </c>
-      <c r="M8" t="n">
-        <v>304</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.06055724913043437</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1037854592728726</v>
-      </c>
-      <c r="P8" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.05059978400514363</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.03154014998847552</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7863,40 +7852,40 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>297</v>
+        <v>7</v>
       </c>
       <c r="X8" t="n">
-        <v>102</v>
+        <v>-16</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.06055724913043437</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1037854592728726</v>
+        <v>-0.1336566183016668</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="AC8" t="n">
-        <v>-213</v>
+        <v>74</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.06446081900614109</v>
+        <v>0.1542767234392135</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.09785206928158402</v>
+        <v>-0.01960125742563762</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.2262394594970895</v>
+        <v>0.1821576248858281</v>
       </c>
       <c r="AH8" t="n">
-        <v>-125</v>
+        <v>37</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -7905,12 +7894,8 @@
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="n">
-        <v>0.05128529554140782</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.04873520817013055</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7955,34 +7940,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44069</v>
+      </c>
+      <c r="M9" t="n">
+        <v>132</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.3018832599149469</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3018832599149469</v>
+      </c>
+      <c r="P9" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1281248599920793</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06786878172373392</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45079</v>
-      </c>
-      <c r="M9" t="n">
-        <v>355</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.231288305099722</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.231288305099722</v>
-      </c>
-      <c r="P9" t="n">
-        <v>354</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1382702215519126</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.09311482455886631</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -7992,40 +7977,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.231288305099722</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.231288305099722</v>
+        <v>-0.3018832599149469</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="AC9" t="n">
-        <v>-60</v>
+        <v>54</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.3008778279738884</v>
+        <v>0.4324251841864841</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.03627739471119322</v>
+        <v>0.003970226339626459</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.05550840352780184</v>
+        <v>0.01393098327254794</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8034,12 +8019,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.05128529554140782</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>0.007178166975881028</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8336,34 +8317,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138081</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138081</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645823</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451878</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -8373,22 +8354,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -8397,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367029</v>
+        <v>0.4792042812088524</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8445,34 +8426,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45125</v>
+      </c>
+      <c r="M3" t="n">
+        <v>385</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2867967086275238</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2867967086275238</v>
+      </c>
+      <c r="P3" t="n">
+        <v>384</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1845225032964088</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1293922192700595</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45751</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45855</v>
-      </c>
-      <c r="M3" t="n">
-        <v>102</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1919673527633516</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1919673527633516</v>
-      </c>
-      <c r="P3" t="n">
-        <v>101</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.08882055381815625</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06105255483079631</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8482,31 +8463,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>58</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1919673527633516</v>
+        <v>-0.2867967086275238</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1919673527633516</v>
+        <v>-0.2867967086275238</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="AC3" t="n">
-        <v>15</v>
+        <v>-88</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2375737582136705</v>
+        <v>0.4021247687677061</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8570,12 +8551,1272 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45167</v>
+      </c>
+      <c r="M4" t="n">
+        <v>415</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2236029749778981</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2622253758368088</v>
+      </c>
+      <c r="P4" t="n">
+        <v>376</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1644849879505295</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1197396830634786</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>197</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.2236029749778981</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.2622253758368088</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>218</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.2880008137222483</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.009652536206580922</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.06319373364962577</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>86</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.9069015013894919</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.4748825853361665</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45244</v>
+      </c>
+      <c r="M5" t="n">
+        <v>469</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2597539727423155</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2622253758368087</v>
+      </c>
+      <c r="P5" t="n">
+        <v>467</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.155126915081858</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1200331647266549</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>197</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>-0.2597539727423155</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>-0.2622253758368087</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>272</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0.3509022178809931</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.009359054543404619</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.02704273588520834</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.9069015013894919</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.1655269949776802</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44588</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45019</v>
+      </c>
+      <c r="M6" t="n">
+        <v>313</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1254104153489787</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1254104153489787</v>
+      </c>
+      <c r="P6" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.07284139588447486</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.04606894378819115</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>17</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-178</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1254104153489787</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1254104153489787</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>296</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1433934471092746</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.08332327548186838</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.1613862932785451</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>164</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.05128529554140782</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.04968647066593979</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44729</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45090</v>
+      </c>
+      <c r="M7" t="n">
+        <v>362</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2504502125606831</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2504502125606831</v>
+      </c>
+      <c r="P7" t="n">
+        <v>361</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1595473300416926</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1084945755197246</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>115</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-80</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.2504502125606831</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.2504502125606831</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>247</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.3341341919611436</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.02089764375033494</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.03634649606684071</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>115</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.05128529554140782</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>0.006526314267764954</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45006</v>
+      </c>
+      <c r="M8" t="n">
+        <v>304</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.06055724913043437</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1037854592728726</v>
+      </c>
+      <c r="P8" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05059978400514363</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.03154014998847552</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>297</v>
+      </c>
+      <c r="X8" t="n">
+        <v>102</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.06055724913043437</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1037854592728726</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-213</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.06446081900614109</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.09785206928158402</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.2262394594970895</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-125</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.05128529554140782</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.04873520817013055</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45079</v>
+      </c>
+      <c r="M9" t="n">
+        <v>355</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.231288305099722</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.231288305099722</v>
+      </c>
+      <c r="P9" t="n">
+        <v>354</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1382702215519126</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09311482455886631</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>195</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>-0.231288305099722</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-0.231288305099722</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-60</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0.3008778279738884</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.03627739471119322</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.05550840352780184</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.05128529554140782</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>0.007178166975881028</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AO9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451878</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367029</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45751</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45855</v>
+      </c>
+      <c r="M3" t="n">
+        <v>102</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1919673527633516</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1919673527633516</v>
+      </c>
+      <c r="P3" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.08882055381815625</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06105255483079631</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>32</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1919673527633516</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1919673527633516</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2375737582136705</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>0</v>
@@ -9286,13 +10527,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9398,24 +10639,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -9446,20 +10685,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -9492,20 +10731,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -9541,16 +10784,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -9580,24 +10821,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9628,21 +10867,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9659,37 +10900,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9716,27 +10955,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9763,14 +11000,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -9780,10 +11017,10 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9810,27 +11047,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9857,27 +11094,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9904,27 +11141,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9941,37 +11178,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9988,24 +11225,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -10015,10 +11252,10 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -10045,27 +11282,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -10092,27 +11329,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -10139,27 +11376,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -10186,14 +11423,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -10203,7 +11440,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" s="3" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -10212,6 +11449,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
